--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1477-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1477-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3025F14-FAF9-4CA5-BD02-0C21D125A584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35411880-DD83-4E32-8D19-B247F62BAD0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{495739DD-4C35-420B-AD05-C606763DE354}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C39617AE-B49B-4187-BFC3-14ECD1EB6415}"/>
   </bookViews>
   <sheets>
     <sheet name="1477-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1598,30 +1598,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BAD3474-0D8C-4E05-A264-75C7B315C45E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6BFB041-D196-4C7F-84AB-35BCDBA4D35C}">
   <dimension ref="A1:X36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="7" width="6.75" customWidth="1"/>
-    <col min="8" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" customWidth="1"/>
+    <col min="8" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1691,7 +1691,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1811,7 +1811,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1957,7 +1957,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="41">
         <v>2024</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>6.92</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2177,7 +2177,7 @@
         <v>2.37</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2023</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>5.47</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="41">
         <v>2022</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>7.21</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2021</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>7.09</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="41">
         <v>2020</v>
       </c>
@@ -2465,7 +2465,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2019</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="41">
         <v>2018</v>
       </c>
@@ -2609,7 +2609,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2017</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="41">
         <v>2016</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2015</v>
       </c>
@@ -2825,7 +2825,7 @@
         <v>9.5299999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="41">
         <v>2014</v>
       </c>
@@ -2897,7 +2897,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2013</v>
       </c>
@@ -2969,7 +2969,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="41">
         <v>2012</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>6.79</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2011</v>
       </c>
@@ -3113,7 +3113,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2010</v>
       </c>
@@ -3185,7 +3185,7 @@
         <v>7.22</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="39">
         <v>2009</v>
       </c>
@@ -3257,7 +3257,7 @@
         <v>9.07</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="41">
         <v>2008</v>
       </c>
@@ -3329,7 +3329,7 @@
         <v>8.7200000000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="39">
         <v>2007</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>28.6</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="43">
         <v>2006</v>
       </c>
@@ -3473,7 +3473,7 @@
         <v>7.82</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="45"/>
       <c r="B28" s="46"/>
       <c r="C28" s="20" t="s">
@@ -3501,7 +3501,7 @@
       <c r="W28" s="54"/>
       <c r="X28" s="48"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2005</v>
       </c>
@@ -3573,7 +3573,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="41">
         <v>2004</v>
       </c>
@@ -3645,7 +3645,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2003</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>2002</v>
       </c>
@@ -3789,7 +3789,7 @@
         <v>9.14</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="55">
         <v>2001</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="57"/>
       <c r="B34" s="58"/>
       <c r="C34" s="22" t="s">
@@ -3889,7 +3889,7 @@
       <c r="W34" s="64"/>
       <c r="X34" s="60"/>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="41">
         <v>2000</v>
       </c>
@@ -3961,7 +3961,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="39" t="s">
         <v>61</v>
       </c>
